--- a/data_extactor/batch_10_fa/trimmed/batch_0053_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0053_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | نظارت | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | نظارت | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امور اداری و دفتری | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
+          <t>زبان انگلیسی | اداری | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | تشخیص گفتار | بیان کتبی | دید نزدیک | مرتب‌سازی اطلاعات | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | تشخیص گفتار | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تندنویسان و ثبت‌کنندگان هم‌زمان جلسات دادگاه | بایگان‌ها و کارمندان امور اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌های پزشکی و مسئولان دفاتر درمانی | متصدیان پذیرش و کارمندان اطلاعات | تایپیست‌ها و متصدیان پردازش متن</t>
+          <t>تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | متصدیان بایگانی و اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان پذیرش و اطلاعات | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | وضوح گفتار | بیان شفاهی | تشخیص گفتار | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | وضوح گفتار | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارشناسان پاسخگویی و خدمات مشتریان | منشی‌های پزشکی و مسئولان دفاتر درمانی | کارمندان امور اداری و دفتری | داروسازان | تکنسین‌های دارویی | فروشندگان خرده‌فروشی</t>
+          <t>صندوق‌داران | کارشناسان خدمات و پشتیبانی مشتریان | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | داروسازان | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | فروشندگان خرده‌فروشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | امور اداری و دفتری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | اداری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی دستی | دید نزدیک | قدرت تنه</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت دستی | بینایی نزدیک | قدرت تنه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مراقبان و نگهداران حیوانات | کارشناسان و تکنسین‌های آزمایشگاه‌های بالینی و پاتولوژی | کارشناسان خون‌گیری (فلبوتومیست‌ها) | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
+          <t>مراقبان و نگهداران حیوانات | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های خون‌گیری | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | حساسیت به مسئله | درک کتبی | درک شفاهی | بیان شفاهی | چابکی انگشتان</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | درک شفاهی | بیان شفاهی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان و تکنسین‌های آزمایشگاه‌های بالینی و پاتولوژی | کمک‌بهیاران | تکنسین‌ها و کارشناسان رادیولوژی و فناوری‌های پرتوشناختی</t>
+          <t>تکنسین‌های فوریت‌های پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کمک‌پرستاران | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کمک‌بهیاران | مراقبان سلامت در منزل | مراقبان خدمات شخصی | دستیاران پزشک | دستیاران فیزیوتراپی | دستیاران کاردرمانی | کارشناسان خون‌گیری (فلبوتومیست‌ها)</t>
+          <t>کمک‌پرستاران | مراقبان سلامت و بهیاران مراقبت در منزل | مراقبان خدمات شخصی و همراهان توان‌خواهان | کمک‌پزشکان و دستیاران مطب | کمک‌یاران فیزیوتراپی | کمک‌یاران کاردرمانی | کارشناسان و تکنسین‌های خون‌گیری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | درمان و مشاوره‌های توانبخشی | روان‌شناسی | خدمات مشتریان و خدمات فردی | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان (ادیولوژیست‌ها) | متخصصان تجویز سمعک و ارزیابی شنوایی | کاردرمانگران | دستیاران کاردرمانی | دستیاران فیزیوتراپی | تکنسین‌های خدمات سلامت روان و روان‌پزشکی | کارشناسان و آسیب‌شناسان گفتار و زبان (گفتاردرمانگران)</t>
+          <t>شنوایی‌شناسان | کارشناسان تجویز و ساخت سمعک | کاردرمانگران | کمک‌یاران کاردرمانی | کمک‌یاران فیزیوتراپی | تکنسین‌های روان‌پزشکی و بهداشت روان | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | آموزش و تدریس | رایانه و الکترونیک | تولید و فرآوری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | رایانه و الکترونیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | درک کتبی | پایداری دست و بازو | چابکی انگشتان</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | تکنسین‌ها و کارشناسان فناوری قلب و عروق | دستیاران پزشک | تکنسین‌های آماده‌سازی و استریلیزاسیون تجهیزات پزشکی | تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | دستیاران اتاق عمل و جراحی | تکنسین‌های اتاق عمل</t>
+          <t>دستیاران متخصص بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | مدیریت و امور اداری | روان‌شناسی | آموزش و تدریس | امور پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | روان‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ماموران مراقبت و زندان‌بانان | کارآگاهان و بازرسان کشف جرایم | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول نگهبانان و ماموران حراست | ماموران گشت پلیس و کلانتری | افسران مراقبت‌های پس از خروج و مددکاران بازپروری زندانیان | پلیس خطوط ریلی و سامانه‌های ترانزیت</t>
+          <t>مأموران زندان و بازداشتگاه | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران گشت پلیس و کلانتری | مددکاران قضایی و متخصصان اصلاح و تربیت | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | روان‌شناسی | امور پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | روان‌شناسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ماموران مراقبت و زندان‌بانان | کارآگاهان و بازرسان کشف جرایم | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول نگهبانان و ماموران حراست | تحلیل‌گران داده‌های اطلاعاتی و امنیتی | ماموران گشت پلیس و کلانتری | پلیس خطوط ریلی و سامانه‌های ترانزیت</t>
+          <t>مأموران زندان و بازداشتگاه | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول کارکنان حراست و انتظامات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | ماموران گشت پلیس و کلانتری | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | آموزش و تدریس | ساختمان و سازه | مدیریت و امور اداری | مکانیک | امور پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | آموزش و پرورش | ساختمان و ساخت‌وساز | مدیریت و اداره | مکانیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بازرسان و کارشناسان بررسی علل حریق و حوادث | مهندسان ایمنی و حفاظت در برابر حریق | آتش‌نشانان | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول نگهبانان و ماموران حراست | بازرسان و کارشناسان پیشگیری از حریق در جنگل‌ها و مراتع | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | آتش‌نشانان | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
